--- a/Requirments/SIQs.xlsx
+++ b/Requirments/SIQs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITI\QA\Project\QA-project-tool\Requirments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE20DC7-FF76-4CB6-93AB-CC9819CE5E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F427BF40-393A-413E-8D4E-76176E886E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Question</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t>Answer(Name,Date, Comment)</t>
+  </si>
+  <si>
+    <t>Feature</t>
   </si>
 </sst>
 </file>
@@ -164,7 +167,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
@@ -189,30 +192,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -492,29 +471,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.42578125" customWidth="1"/>
-    <col min="2" max="2" width="57" customWidth="1"/>
-    <col min="3" max="3" width="45.42578125" customWidth="1"/>
-    <col min="4" max="4" width="43.42578125" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" customWidth="1"/>
+    <col min="3" max="3" width="57" customWidth="1"/>
+    <col min="4" max="4" width="45.42578125" customWidth="1"/>
+    <col min="5" max="5" width="43.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="5" customFormat="1" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" s="5" customFormat="1" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -537,9 +519,19 @@
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D1048576">
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"Approved"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"In Disscusion"</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -550,18 +542,9 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
-      <formula>"In Disscusion"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"N/A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"Approved"</formula>
-    </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{E5A70537-E00A-4E3C-8A84-DCB9E24EA7C9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{E5A70537-E00A-4E3C-8A84-DCB9E24EA7C9}">
       <formula1>"In Disscusion, Approved, N/A"</formula1>
     </dataValidation>
   </dataValidations>
